--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
@@ -612,7 +612,7 @@
         <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R2" t="n">
         <v>-0.1</v>
@@ -723,7 +723,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -733,75 +733,79 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="H4" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="I4" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="J4" t="n">
-        <v>19.8</v>
+        <v>31.5</v>
       </c>
       <c r="K4" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>38.2</v>
+        <v>57.8</v>
       </c>
       <c r="M4" t="n">
-        <v>43.7</v>
+        <v>51.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.5</v>
+        <v>6.5</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.3</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>16.6 (5g)</t>
+        </is>
+      </c>
       <c r="X4" t="n">
-        <v>-6.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -815,55 +819,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7</v>
+        <v>23.3</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2</v>
+        <v>23.4</v>
       </c>
       <c r="G5" t="n">
-        <v>14.3</v>
+        <v>22.4</v>
       </c>
       <c r="H5" t="n">
-        <v>12.6</v>
+        <v>22.4</v>
       </c>
       <c r="I5" t="n">
-        <v>11.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="K5" t="n">
-        <v>31.8</v>
+        <v>33.7</v>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>52.7</v>
       </c>
       <c r="M5" t="n">
-        <v>52.4</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
+        <v>80</v>
+      </c>
+      <c r="P5" t="n">
         <v>70</v>
       </c>
-      <c r="P5" t="n">
-        <v>65</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="U5" t="n">
         <v>4</v>
@@ -873,17 +877,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>12.0 (7g)</t>
+          <t>16.5 (4g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -897,55 +901,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E6" t="n">
-        <v>8.300000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>23.8</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4</v>
+        <v>24.6</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9</v>
+        <v>22.9</v>
       </c>
       <c r="I6" t="n">
-        <v>12.2</v>
+        <v>23.2</v>
       </c>
       <c r="J6" t="n">
-        <v>31.5</v>
+        <v>35.8</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>35.7</v>
       </c>
       <c r="L6" t="n">
-        <v>57.8</v>
+        <v>45.9</v>
       </c>
       <c r="M6" t="n">
-        <v>51.3</v>
+        <v>43.8</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>-1</v>
+        <v>0.6</v>
       </c>
       <c r="S6" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>20</v>
@@ -955,17 +959,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>16.6 (5g)</t>
+          <t>27.2 (6g)</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -975,79 +979,79 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>18.2</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="I7" t="n">
-        <v>8.699999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="J7" t="n">
-        <v>16.8</v>
+        <v>29.2</v>
       </c>
       <c r="K7" t="n">
-        <v>20.7</v>
+        <v>29.1</v>
       </c>
       <c r="L7" t="n">
-        <v>60.7</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="n">
-        <v>48.7</v>
+        <v>45.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
         <v>60</v>
       </c>
       <c r="P7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.9</v>
+        <v>-0.6</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>27</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13.2 (6g)</t>
+          <t>10.3 (3g)</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1057,79 +1061,79 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.5</v>
+        <v>19.5</v>
       </c>
       <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24.6</v>
-      </c>
       <c r="H8" t="n">
-        <v>22.9</v>
+        <v>20.7</v>
       </c>
       <c r="I8" t="n">
-        <v>23.2</v>
+        <v>19.4</v>
       </c>
       <c r="J8" t="n">
-        <v>35.8</v>
+        <v>29.2</v>
       </c>
       <c r="K8" t="n">
-        <v>35.7</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>45.9</v>
+        <v>54.9</v>
       </c>
       <c r="M8" t="n">
-        <v>43.8</v>
+        <v>55.2</v>
       </c>
       <c r="N8" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
+        <v>70</v>
+      </c>
+      <c r="P8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>45</v>
-      </c>
       <c r="Q8" t="n">
-        <v>-2.3</v>
+        <v>-0.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="U8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
         <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>27.2 (6g)</t>
+          <t>29.3 (6g)</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1143,75 +1147,75 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="E9" t="n">
-        <v>23.3</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>23.4</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>22.4</v>
+        <v>8.1</v>
       </c>
       <c r="H9" t="n">
-        <v>22.4</v>
+        <v>10.1</v>
       </c>
       <c r="I9" t="n">
-        <v>21.1</v>
+        <v>10.2</v>
       </c>
       <c r="J9" t="n">
-        <v>32.8</v>
+        <v>24.5</v>
       </c>
       <c r="K9" t="n">
-        <v>33.7</v>
+        <v>24.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52.7</v>
+        <v>39.2</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>43.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P9" t="n">
         <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>-3</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>-4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9</v>
+        <v>-0</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>16.5 (4g)</t>
+          <t>6.3 (3g)</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1221,79 +1225,75 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>11.3</v>
       </c>
       <c r="F10" t="n">
-        <v>18.2</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>19.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>18.3</v>
+        <v>10.8</v>
       </c>
       <c r="I10" t="n">
-        <v>18.8</v>
+        <v>11.6</v>
       </c>
       <c r="J10" t="n">
-        <v>29.2</v>
+        <v>19.8</v>
       </c>
       <c r="K10" t="n">
-        <v>29.1</v>
+        <v>22.1</v>
       </c>
       <c r="L10" t="n">
-        <v>50.9</v>
+        <v>38.2</v>
       </c>
       <c r="M10" t="n">
-        <v>45.5</v>
+        <v>43.7</v>
       </c>
       <c r="N10" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6</v>
+        <v>-2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
         <v>27</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>10.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-15.8</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1303,79 +1303,79 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>11.5</v>
       </c>
       <c r="E11" t="n">
-        <v>18.7</v>
+        <v>14.7</v>
       </c>
       <c r="F11" t="n">
-        <v>22.2</v>
+        <v>13.2</v>
       </c>
       <c r="G11" t="n">
-        <v>21.6</v>
+        <v>14.3</v>
       </c>
       <c r="H11" t="n">
-        <v>21.2</v>
+        <v>12.6</v>
       </c>
       <c r="I11" t="n">
-        <v>22.3</v>
+        <v>11.9</v>
       </c>
       <c r="J11" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
       <c r="K11" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
       </c>
       <c r="L11" t="n">
-        <v>48.6</v>
+        <v>56.4</v>
       </c>
       <c r="M11" t="n">
-        <v>46.2</v>
+        <v>52.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P11" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
         <v>27</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>18.6 (5g)</t>
+          <t>12.0 (7g)</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-5.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1385,79 +1385,79 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>14.4</v>
+        <v>6.8</v>
       </c>
       <c r="G12" t="n">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="H12" t="n">
-        <v>11.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>31.5</v>
+        <v>16.8</v>
       </c>
       <c r="K12" t="n">
-        <v>31.1</v>
+        <v>20.7</v>
       </c>
       <c r="L12" t="n">
-        <v>47.5</v>
+        <v>60.7</v>
       </c>
       <c r="M12" t="n">
-        <v>45.6</v>
+        <v>48.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4</v>
+        <v>-3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>16.9 (7g)</t>
+          <t>13.2 (6g)</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1467,79 +1467,79 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="F13" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="G13" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="H13" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="I13" t="n">
-        <v>19.4</v>
+        <v>22.3</v>
       </c>
       <c r="J13" t="n">
-        <v>29.2</v>
+        <v>35.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>35.1</v>
       </c>
       <c r="L13" t="n">
-        <v>54.9</v>
+        <v>48.6</v>
       </c>
       <c r="M13" t="n">
-        <v>55.2</v>
+        <v>46.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="S13" t="n">
-        <v>-0.4</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>29.3 (6g)</t>
+          <t>18.6 (5g)</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1553,55 +1553,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>14.3</v>
       </c>
       <c r="F14" t="n">
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="H14" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>12.7</v>
       </c>
       <c r="J14" t="n">
-        <v>24.5</v>
+        <v>31.5</v>
       </c>
       <c r="K14" t="n">
-        <v>24.5</v>
+        <v>31.1</v>
       </c>
       <c r="L14" t="n">
-        <v>39.2</v>
+        <v>47.5</v>
       </c>
       <c r="M14" t="n">
-        <v>43.7</v>
+        <v>45.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.7</v>
       </c>
-      <c r="R14" t="n">
-        <v>-3</v>
-      </c>
       <c r="S14" t="n">
-        <v>-4.5</v>
+        <v>1.9</v>
       </c>
       <c r="T14" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="U14" t="n">
         <v>20</v>
@@ -1611,17 +1611,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.3 (3g)</t>
+          <t>16.9 (7g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1635,75 +1635,75 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="G15" t="n">
-        <v>13.1</v>
+        <v>21.3</v>
       </c>
       <c r="H15" t="n">
-        <v>13.2</v>
+        <v>23.4</v>
       </c>
       <c r="I15" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="J15" t="n">
-        <v>26.1</v>
+        <v>34.1</v>
       </c>
       <c r="K15" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="L15" t="n">
-        <v>52.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="n">
-        <v>46.5</v>
+        <v>43.8</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="O15" t="n">
         <v>40</v>
       </c>
       <c r="P15" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2</v>
+        <v>-8.4</v>
       </c>
       <c r="S15" t="n">
-        <v>6.4</v>
+        <v>-4</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>15.2 (6g)</t>
+          <t>26.7 (3g)</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1713,79 +1713,79 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>9.5</v>
       </c>
       <c r="E16" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="G16" t="n">
-        <v>9.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>11.3</v>
       </c>
       <c r="J16" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="K16" t="n">
-        <v>26.1</v>
+        <v>27.7</v>
       </c>
       <c r="L16" t="n">
-        <v>54.9</v>
+        <v>45.6</v>
       </c>
       <c r="M16" t="n">
-        <v>52.6</v>
+        <v>44.6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>-1.2</v>
       </c>
       <c r="U16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V16" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>10.2 (5g)</t>
+          <t>9.2 (6g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>-5.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1795,79 +1795,79 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
       <c r="E17" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="F17" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="G17" t="n">
-        <v>22.2</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>23.2</v>
+        <v>13.8</v>
       </c>
       <c r="I17" t="n">
-        <v>22.7</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>33.9</v>
+        <v>29.7</v>
       </c>
       <c r="K17" t="n">
-        <v>35.3</v>
+        <v>29</v>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>56.4</v>
       </c>
       <c r="M17" t="n">
-        <v>44</v>
+        <v>52.9</v>
       </c>
       <c r="N17" t="n">
-        <v>11.2</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>-6.9</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4</v>
+        <v>0.7</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
         <v>20</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>26.7 (3g)</t>
+          <t>9.2 (5g)</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1877,79 +1877,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E18" t="n">
         <v>12.3</v>
       </c>
       <c r="F18" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>13.5</v>
+        <v>12.3</v>
       </c>
       <c r="H18" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="I18" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="J18" t="n">
-        <v>27.9</v>
+        <v>30.5</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L18" t="n">
-        <v>46.4</v>
+        <v>41.7</v>
       </c>
       <c r="M18" t="n">
-        <v>44.8</v>
+        <v>41.7</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.6</v>
       </c>
-      <c r="T18" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>20</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>9.2 (6g)</t>
+          <t>11.7 (6g)</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>10.3</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1959,79 +1959,79 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K19" t="n">
         <v>19</v>
       </c>
-      <c r="F19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>28.9</v>
-      </c>
       <c r="L19" t="n">
-        <v>53.8</v>
+        <v>39.6</v>
       </c>
       <c r="M19" t="n">
-        <v>51.7</v>
+        <v>35.3</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P19" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>-1.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
         <v>20</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>9.2 (5g)</t>
+          <t>4.2 (5g)</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2045,55 +2045,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="E20" t="n">
-        <v>15.3</v>
+        <v>22.7</v>
       </c>
       <c r="F20" t="n">
-        <v>13.4</v>
+        <v>21.2</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6</v>
+        <v>19.9</v>
       </c>
       <c r="H20" t="n">
-        <v>13.4</v>
+        <v>20.8</v>
       </c>
       <c r="I20" t="n">
-        <v>12.7</v>
+        <v>22.1</v>
       </c>
       <c r="J20" t="n">
-        <v>30.6</v>
+        <v>32.8</v>
       </c>
       <c r="K20" t="n">
-        <v>28.5</v>
+        <v>33.9</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1</v>
+        <v>45.1</v>
       </c>
       <c r="M20" t="n">
-        <v>43.2</v>
+        <v>51.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>-0</v>
+        <v>-6.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="U20" t="n">
         <v>4</v>
@@ -2103,17 +2103,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>11.7 (6g)</t>
+          <t>21.2 (5g)</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>-10.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2123,79 +2123,79 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
       <c r="E21" t="n">
-        <v>8.300000000000001</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>10.6</v>
+        <v>21.8</v>
       </c>
       <c r="G21" t="n">
-        <v>10.8</v>
+        <v>23.8</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>22.4</v>
       </c>
       <c r="I21" t="n">
-        <v>8.199999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="J21" t="n">
-        <v>24.8</v>
+        <v>31.3</v>
       </c>
       <c r="K21" t="n">
-        <v>20.7</v>
+        <v>28.5</v>
       </c>
       <c r="L21" t="n">
-        <v>45.9</v>
+        <v>66.7</v>
       </c>
       <c r="M21" t="n">
-        <v>39.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P21" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="S21" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V21" t="n">
         <v>29</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>11.0 (4g)</t>
+          <t>14.7 (6g)</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>5.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,79 +2205,79 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>18.2</v>
       </c>
       <c r="G22" t="n">
-        <v>11.1</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>12.9</v>
       </c>
       <c r="I22" t="n">
-        <v>9.199999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="J22" t="n">
-        <v>18.2</v>
+        <v>35.8</v>
       </c>
       <c r="K22" t="n">
-        <v>15.4</v>
+        <v>24.3</v>
       </c>
       <c r="L22" t="n">
-        <v>63.8</v>
+        <v>45.2</v>
       </c>
       <c r="M22" t="n">
-        <v>62</v>
+        <v>40.2</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
         <v>60</v>
       </c>
       <c r="P22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3</v>
+        <v>-5.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>29</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.2 (5g)</t>
+          <t>0.7 (3g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>21.9</v>
+        <v>-38.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2287,79 +2287,79 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>21.8</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>23.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>22.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>21.5</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>31.3</v>
+        <v>28.3</v>
       </c>
       <c r="K23" t="n">
-        <v>28.5</v>
+        <v>26.1</v>
       </c>
       <c r="L23" t="n">
-        <v>66.7</v>
+        <v>54.9</v>
       </c>
       <c r="M23" t="n">
-        <v>66.09999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P23" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V23" t="n">
         <v>29</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>14.7 (6g)</t>
+          <t>10.2 (5g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-1.6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2373,75 +2373,75 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E24" t="n">
-        <v>11.7</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>11.8</v>
       </c>
       <c r="H24" t="n">
-        <v>20.1</v>
+        <v>11.3</v>
       </c>
       <c r="I24" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="J24" t="n">
-        <v>23.7</v>
+        <v>27.1</v>
       </c>
       <c r="K24" t="n">
-        <v>30.9</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
-        <v>49.9</v>
+        <v>43.7</v>
       </c>
       <c r="M24" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P24" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>-8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.2</v>
+        <v>1.1</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>26.2 (4g)</t>
+          <t>7.9 (7g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1.5</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2451,79 +2451,79 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>13.1</v>
       </c>
       <c r="H25" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="I25" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="J25" t="n">
-        <v>35.8</v>
+        <v>26.1</v>
       </c>
       <c r="K25" t="n">
-        <v>24.3</v>
+        <v>28.5</v>
       </c>
       <c r="L25" t="n">
-        <v>45.2</v>
+        <v>52.8</v>
       </c>
       <c r="M25" t="n">
-        <v>40.2</v>
+        <v>46.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O25" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P25" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.9</v>
+        <v>-1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>6.6</v>
+        <v>-0.2</v>
       </c>
       <c r="S25" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="T25" t="n">
-        <v>11.5</v>
+        <v>-2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
         <v>29</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.7 (3g)</t>
+          <t>15.2 (6g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-38.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2537,55 +2537,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="H26" t="n">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="I26" t="n">
-        <v>12.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>27.1</v>
+        <v>18.2</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>15.4</v>
       </c>
       <c r="L26" t="n">
-        <v>43.7</v>
+        <v>63.8</v>
       </c>
       <c r="M26" t="n">
-        <v>46.3</v>
+        <v>62</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P26" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S26" t="n">
         <v>1.8</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-2.6</v>
-      </c>
       <c r="T26" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>8</v>
@@ -2595,17 +2595,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>7.9 (7g)</t>
+          <t>2.2 (5g)</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>-10.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2619,75 +2619,75 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="H27" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>20.6</v>
+        <v>24.8</v>
       </c>
       <c r="K27" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>37.7</v>
+        <v>45.9</v>
       </c>
       <c r="M27" t="n">
-        <v>36.8</v>
+        <v>39.5</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="V27" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>4.2 (5g)</t>
+          <t>11.0 (4g)</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>-1.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2697,73 +2697,73 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
       <c r="E28" t="n">
-        <v>20.7</v>
+        <v>13.7</v>
       </c>
       <c r="F28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>20.4</v>
       </c>
-      <c r="G28" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I28" t="n">
-        <v>22</v>
-      </c>
       <c r="J28" t="n">
-        <v>33</v>
+        <v>22.5</v>
       </c>
       <c r="K28" t="n">
-        <v>34</v>
+        <v>30.4</v>
       </c>
       <c r="L28" t="n">
-        <v>46.4</v>
+        <v>47.8</v>
       </c>
       <c r="M28" t="n">
-        <v>52.2</v>
+        <v>48.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="O28" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P28" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>10.9</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.6</v>
+        <v>-8.4</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.8</v>
+        <v>-0.3</v>
       </c>
       <c r="T28" t="n">
-        <v>-1</v>
+        <v>-7.9</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
         <v>20</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>21.2 (5g)</t>
+          <t>26.2 (4g)</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>-3.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="29">
@@ -2868,52 +2868,52 @@
         <v>19.5</v>
       </c>
       <c r="E30" t="n">
-        <v>16.3</v>
+        <v>21.3</v>
       </c>
       <c r="F30" t="n">
-        <v>16.8</v>
+        <v>18.8</v>
       </c>
       <c r="G30" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="H30" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="I30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="K30" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="L30" t="n">
-        <v>47.4</v>
+        <v>48.8</v>
       </c>
       <c r="M30" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="N30" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P30" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.3</v>
+        <v>-2.2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="U30" t="n">
         <v>22</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="31">
@@ -3032,52 +3032,52 @@
         <v>11.5</v>
       </c>
       <c r="E32" t="n">
-        <v>21.3</v>
+        <v>13</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="G32" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H32" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="I32" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="K32" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="L32" t="n">
-        <v>46.6</v>
+        <v>43.4</v>
       </c>
       <c r="M32" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
       <c r="N32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
         <v>40</v>
       </c>
       <c r="P32" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S32" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>22</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="33">
@@ -3110,52 +3110,52 @@
         <v>25.5</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="F33" t="n">
-        <v>20.6</v>
+        <v>22.6</v>
       </c>
       <c r="G33" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="H33" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="I33" t="n">
-        <v>25.2</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="K33" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="L33" t="n">
-        <v>45.2</v>
+        <v>44.2</v>
       </c>
       <c r="M33" t="n">
-        <v>44.9</v>
+        <v>45.9</v>
       </c>
       <c r="N33" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="O33" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P33" t="n">
         <v>50</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>-4.6</v>
+        <v>-3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="U33" t="n">
         <v>22</v>
@@ -3171,12 +3171,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3185,76 +3185,76 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H34" t="n">
         <v>14.5</v>
       </c>
-      <c r="E34" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F34" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G34" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I34" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J34" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>25.7</v>
+        <v>31.5</v>
       </c>
       <c r="L34" t="n">
-        <v>52.6</v>
+        <v>44.4</v>
       </c>
       <c r="M34" t="n">
-        <v>53.6</v>
+        <v>44</v>
       </c>
       <c r="N34" t="n">
-        <v>5.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O34" t="n">
+        <v>60</v>
+      </c>
+      <c r="P34" t="n">
         <v>70</v>
       </c>
-      <c r="P34" t="n">
-        <v>65</v>
-      </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>-36.8</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3263,71 +3263,75 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>18.3</v>
       </c>
       <c r="F35" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="H35" t="n">
-        <v>12.2</v>
+        <v>16.8</v>
       </c>
       <c r="I35" t="n">
-        <v>13.2</v>
+        <v>16.5</v>
       </c>
       <c r="J35" t="n">
-        <v>25.4</v>
+        <v>30.5</v>
       </c>
       <c r="K35" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>49.3</v>
       </c>
       <c r="M35" t="n">
-        <v>45.7</v>
+        <v>50.4</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.3</v>
+        <v>-2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>16.3 (3g)</t>
+        </is>
+      </c>
       <c r="X35" t="n">
-        <v>-1.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3337,59 +3341,59 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="n">
-        <v>27.3</v>
+        <v>16.7</v>
       </c>
       <c r="F36" t="n">
-        <v>25.4</v>
+        <v>15.2</v>
       </c>
       <c r="G36" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="H36" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="I36" t="n">
-        <v>18.2</v>
+        <v>16.9</v>
       </c>
       <c r="J36" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="K36" t="n">
-        <v>31.7</v>
+        <v>33.6</v>
       </c>
       <c r="L36" t="n">
-        <v>46.8</v>
+        <v>51.5</v>
       </c>
       <c r="M36" t="n">
-        <v>43.6</v>
+        <v>45.2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="O36" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P36" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="R36" t="n">
-        <v>7.2</v>
+        <v>-1.7</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U36" t="n">
         <v>8</v>
@@ -3399,13 +3403,13 @@
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>-4.6</v>
+        <v>-25.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3415,59 +3419,59 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="G37" t="n">
-        <v>14.1</v>
+        <v>25.9</v>
       </c>
       <c r="H37" t="n">
-        <v>14.5</v>
+        <v>27.2</v>
       </c>
       <c r="I37" t="n">
-        <v>14.5</v>
+        <v>25.8</v>
       </c>
       <c r="J37" t="n">
-        <v>29</v>
+        <v>37.1</v>
       </c>
       <c r="K37" t="n">
-        <v>31.5</v>
+        <v>36.6</v>
       </c>
       <c r="L37" t="n">
-        <v>44.4</v>
+        <v>45.4</v>
       </c>
       <c r="M37" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="N37" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P37" t="n">
         <v>70</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.3</v>
+        <v>-1.6</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="T37" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
       </c>
       <c r="U37" t="n">
         <v>8</v>
@@ -3477,13 +3481,13 @@
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>-17.8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3493,79 +3497,79 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="E38" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="G38" t="n">
-        <v>12.7</v>
+        <v>15</v>
       </c>
       <c r="H38" t="n">
-        <v>11.8</v>
+        <v>16.9</v>
       </c>
       <c r="I38" t="n">
-        <v>10.9</v>
+        <v>16.3</v>
       </c>
       <c r="J38" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="K38" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="L38" t="n">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="P38" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="R38" t="n">
-        <v>3.1</v>
+        <v>-3.1</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>-1.3</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="U38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V38" t="n">
         <v>23</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>10.3 (3g)</t>
+          <t>21.7 (3g)</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>4.5</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3575,79 +3579,75 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="E39" t="n">
-        <v>18.3</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>19.6</v>
+        <v>5.6</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3</v>
+        <v>5.8</v>
       </c>
       <c r="H39" t="n">
-        <v>16.8</v>
+        <v>7.2</v>
       </c>
       <c r="I39" t="n">
-        <v>16.5</v>
+        <v>7.9</v>
       </c>
       <c r="J39" t="n">
-        <v>30.5</v>
+        <v>22.1</v>
       </c>
       <c r="K39" t="n">
-        <v>28.6</v>
+        <v>24.6</v>
       </c>
       <c r="L39" t="n">
-        <v>49.3</v>
+        <v>58.3</v>
       </c>
       <c r="M39" t="n">
-        <v>50.4</v>
+        <v>51.6</v>
       </c>
       <c r="N39" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>60</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q39" t="n">
-        <v>-2</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="S39" t="n">
-        <v>-1.1</v>
+        <v>6.7</v>
       </c>
       <c r="T39" t="n">
-        <v>1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V39" t="n">
-        <v>23</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>16.3 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>11.2</v>
+        <v>-33.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3657,79 +3657,75 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
       <c r="E40" t="n">
-        <v>13.3</v>
+        <v>38.7</v>
       </c>
       <c r="F40" t="n">
-        <v>12.4</v>
+        <v>31.6</v>
       </c>
       <c r="G40" t="n">
-        <v>12.8</v>
+        <v>27.7</v>
       </c>
       <c r="H40" t="n">
-        <v>14.3</v>
+        <v>26.1</v>
       </c>
       <c r="I40" t="n">
-        <v>13.1</v>
+        <v>25.6</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
-        <v>42.7</v>
+        <v>50.9</v>
       </c>
       <c r="M40" t="n">
-        <v>44.7</v>
+        <v>50.6</v>
       </c>
       <c r="N40" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.4</v>
+        <v>-2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.7</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>-1.9</v>
+        <v>0.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V40" t="n">
         <v>23</v>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>19.0 (3g)</t>
-        </is>
-      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
-        <v>12.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3739,75 +3735,79 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>12.5</v>
       </c>
       <c r="E41" t="n">
-        <v>16.7</v>
+        <v>11.3</v>
       </c>
       <c r="F41" t="n">
-        <v>15.2</v>
+        <v>13</v>
       </c>
       <c r="G41" t="n">
-        <v>20.2</v>
+        <v>14.9</v>
       </c>
       <c r="H41" t="n">
-        <v>18.8</v>
+        <v>12.4</v>
       </c>
       <c r="I41" t="n">
-        <v>16.9</v>
+        <v>12.3</v>
       </c>
       <c r="J41" t="n">
-        <v>33.5</v>
+        <v>23.1</v>
       </c>
       <c r="K41" t="n">
-        <v>33.6</v>
+        <v>22.1</v>
       </c>
       <c r="L41" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="M41" t="n">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="N41" t="n">
-        <v>10.2</v>
+        <v>5.3</v>
       </c>
       <c r="O41" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P41" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.7</v>
+        <v>0.7</v>
       </c>
       <c r="S41" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>11.3 (3g)</t>
+        </is>
+      </c>
       <c r="X41" t="n">
-        <v>-25.8</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3821,71 +3821,71 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.5</v>
+        <v>11.5</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
+        <v>14.7</v>
       </c>
       <c r="F42" t="n">
-        <v>24.2</v>
+        <v>14.2</v>
       </c>
       <c r="G42" t="n">
-        <v>25.9</v>
+        <v>14.6</v>
       </c>
       <c r="H42" t="n">
-        <v>27.2</v>
+        <v>13.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25.8</v>
+        <v>13.3</v>
       </c>
       <c r="J42" t="n">
-        <v>37.1</v>
+        <v>23.5</v>
       </c>
       <c r="K42" t="n">
-        <v>36.6</v>
+        <v>23.6</v>
       </c>
       <c r="L42" t="n">
-        <v>45.4</v>
+        <v>59.5</v>
       </c>
       <c r="M42" t="n">
-        <v>44.2</v>
+        <v>57.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.6</v>
+        <v>0.9</v>
       </c>
       <c r="S42" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>-2</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3895,79 +3895,75 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="E43" t="n">
-        <v>15.7</v>
+        <v>27.3</v>
       </c>
       <c r="F43" t="n">
-        <v>13.2</v>
+        <v>25.4</v>
       </c>
       <c r="G43" t="n">
-        <v>15</v>
+        <v>22.1</v>
       </c>
       <c r="H43" t="n">
-        <v>16.9</v>
+        <v>18.7</v>
       </c>
       <c r="I43" t="n">
-        <v>16.3</v>
+        <v>18.2</v>
       </c>
       <c r="J43" t="n">
-        <v>27.7</v>
+        <v>33.2</v>
       </c>
       <c r="K43" t="n">
-        <v>29</v>
+        <v>31.7</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>46.8</v>
       </c>
       <c r="M43" t="n">
-        <v>50.4</v>
+        <v>43.6</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="O43" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P43" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>-3.1</v>
+        <v>7.2</v>
       </c>
       <c r="S43" t="n">
-        <v>-1.3</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.3</v>
+        <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V43" t="n">
-        <v>23</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>21.7 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
-        <v>15.1</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3981,71 +3977,75 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>15.3</v>
       </c>
       <c r="F44" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>5.8</v>
+        <v>12.7</v>
       </c>
       <c r="H44" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
       <c r="I44" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="J44" t="n">
-        <v>22.1</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="L44" t="n">
-        <v>58.3</v>
+        <v>47.3</v>
       </c>
       <c r="M44" t="n">
-        <v>51.6</v>
+        <v>45</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
+        <v>80</v>
+      </c>
+      <c r="P44" t="n">
         <v>60</v>
       </c>
-      <c r="P44" t="n">
-        <v>70</v>
-      </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.3</v>
+        <v>3.1</v>
       </c>
       <c r="S44" t="n">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="T44" t="n">
-        <v>-2.4</v>
+        <v>0.5</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
-      </c>
-      <c r="W44" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>10.3 (3g)</t>
+        </is>
+      </c>
       <c r="X44" t="n">
-        <v>-33.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4055,75 +4055,79 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
       <c r="E45" t="n">
-        <v>24.7</v>
+        <v>13.3</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
-        <v>29.4</v>
+        <v>12.8</v>
       </c>
       <c r="H45" t="n">
-        <v>29.5</v>
+        <v>14.3</v>
       </c>
       <c r="I45" t="n">
-        <v>28.4</v>
+        <v>13.1</v>
       </c>
       <c r="J45" t="n">
-        <v>33.2</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>33</v>
+        <v>29.3</v>
       </c>
       <c r="L45" t="n">
-        <v>49.9</v>
+        <v>42.7</v>
       </c>
       <c r="M45" t="n">
-        <v>50.4</v>
+        <v>44.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="U45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V45" t="n">
-        <v>9</v>
-      </c>
-      <c r="W45" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>19.0 (3g)</t>
+        </is>
+      </c>
       <c r="X45" t="n">
-        <v>-13.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4133,80 +4137,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="E46" t="n">
-        <v>38.7</v>
+        <v>24.7</v>
       </c>
       <c r="F46" t="n">
-        <v>31.6</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>27.7</v>
+        <v>29.4</v>
       </c>
       <c r="H46" t="n">
-        <v>26.1</v>
+        <v>29.5</v>
       </c>
       <c r="I46" t="n">
-        <v>25.6</v>
+        <v>28.4</v>
       </c>
       <c r="J46" t="n">
-        <v>30</v>
+        <v>33.2</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L46" t="n">
-        <v>50.9</v>
+        <v>49.9</v>
       </c>
       <c r="M46" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="N46" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>50</v>
+      </c>
+      <c r="P46" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>18</v>
+      </c>
+      <c r="V46" t="n">
         <v>9</v>
-      </c>
-      <c r="O46" t="n">
-        <v>40</v>
-      </c>
-      <c r="P46" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>21</v>
-      </c>
-      <c r="V46" t="n">
-        <v>23</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
-        <v>5.9</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4215,153 +4219,157 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E47" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="G47" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="H47" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I47" t="n">
-        <v>12.3</v>
+        <v>15.6</v>
       </c>
       <c r="J47" t="n">
-        <v>23.1</v>
+        <v>28.7</v>
       </c>
       <c r="K47" t="n">
-        <v>22.1</v>
+        <v>27.7</v>
       </c>
       <c r="L47" t="n">
-        <v>50.6</v>
+        <v>44.5</v>
       </c>
       <c r="M47" t="n">
-        <v>47.8</v>
+        <v>45</v>
       </c>
       <c r="N47" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="O47" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P47" t="n">
         <v>50</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7</v>
+        <v>-2.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.8</v>
+        <v>-0.6</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V47" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>11.3 (3g)</t>
+          <t>12.0 (5g)</t>
         </is>
       </c>
       <c r="X47" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E48" t="n">
-        <v>14.7</v>
+        <v>5.3</v>
       </c>
       <c r="F48" t="n">
-        <v>14.2</v>
+        <v>5.2</v>
       </c>
       <c r="G48" t="n">
-        <v>14.6</v>
+        <v>5.8</v>
       </c>
       <c r="H48" t="n">
-        <v>13.2</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="n">
-        <v>13.3</v>
+        <v>7.5</v>
       </c>
       <c r="J48" t="n">
-        <v>23.5</v>
+        <v>17.8</v>
       </c>
       <c r="K48" t="n">
-        <v>23.6</v>
+        <v>17.6</v>
       </c>
       <c r="L48" t="n">
-        <v>59.5</v>
+        <v>60.1</v>
       </c>
       <c r="M48" t="n">
-        <v>57.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.8</v>
+        <v>-0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9</v>
+        <v>-2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>1.9</v>
+        <v>-9.9</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U48" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>23</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>5.5 (4g)</t>
+        </is>
+      </c>
       <c r="X48" t="n">
-        <v>30.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4378,72 +4386,72 @@
         <v>14.5</v>
       </c>
       <c r="E49" t="n">
-        <v>12.7</v>
+        <v>21</v>
       </c>
       <c r="F49" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
       <c r="G49" t="n">
-        <v>14.4</v>
+        <v>17.3</v>
       </c>
       <c r="H49" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="I49" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="J49" t="n">
-        <v>28.7</v>
+        <v>31.7</v>
       </c>
       <c r="K49" t="n">
-        <v>27.7</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>44.5</v>
+        <v>55.3</v>
       </c>
       <c r="M49" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>70</v>
+      </c>
+      <c r="P49" t="n">
         <v>45</v>
       </c>
-      <c r="N49" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O49" t="n">
-        <v>60</v>
-      </c>
-      <c r="P49" t="n">
-        <v>55</v>
-      </c>
       <c r="Q49" t="n">
-        <v>1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="R49" t="n">
-        <v>-2.4</v>
+        <v>2.9</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.6</v>
+        <v>11.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
       <c r="U49" t="n">
         <v>20</v>
       </c>
       <c r="V49" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>12.0 (5g)</t>
+          <t>12.7 (7g)</t>
         </is>
       </c>
       <c r="X49" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4453,79 +4461,79 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="E50" t="n">
-        <v>5.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>5.2</v>
+        <v>10.8</v>
       </c>
       <c r="G50" t="n">
-        <v>5.8</v>
+        <v>12.1</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>12.9</v>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>13.1</v>
       </c>
       <c r="J50" t="n">
-        <v>17.8</v>
+        <v>23.7</v>
       </c>
       <c r="K50" t="n">
-        <v>17.6</v>
+        <v>25.9</v>
       </c>
       <c r="L50" t="n">
-        <v>60.1</v>
+        <v>39.7</v>
       </c>
       <c r="M50" t="n">
-        <v>70.09999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="N50" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="P50" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0</v>
+        <v>1.6</v>
       </c>
       <c r="R50" t="n">
         <v>-2.3</v>
       </c>
       <c r="S50" t="n">
-        <v>-9.9</v>
+        <v>-3.8</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2</v>
+        <v>-2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>5.5 (4g)</t>
+          <t>15.0 (5g)</t>
         </is>
       </c>
       <c r="X50" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4535,79 +4543,79 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="F51" t="n">
-        <v>16.2</v>
+        <v>6.8</v>
       </c>
       <c r="G51" t="n">
-        <v>17.3</v>
+        <v>12.2</v>
       </c>
       <c r="H51" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="J51" t="n">
-        <v>31.7</v>
+        <v>25.8</v>
       </c>
       <c r="K51" t="n">
-        <v>32</v>
+        <v>26.8</v>
       </c>
       <c r="L51" t="n">
-        <v>55.3</v>
+        <v>50</v>
       </c>
       <c r="M51" t="n">
-        <v>44.1</v>
+        <v>50.3</v>
       </c>
       <c r="N51" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P51" t="n">
         <v>45</v>
       </c>
       <c r="Q51" t="n">
-        <v>-2.2</v>
+        <v>0.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.9</v>
+        <v>-6.3</v>
       </c>
       <c r="S51" t="n">
-        <v>11.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="U51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V51" t="n">
         <v>3</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>12.7 (7g)</t>
+          <t>13.2 (6g)</t>
         </is>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,75 +4629,75 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E52" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="F52" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="H52" t="n">
-        <v>12.9</v>
+        <v>7.8</v>
       </c>
       <c r="I52" t="n">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>23.7</v>
+        <v>20.7</v>
       </c>
       <c r="K52" t="n">
-        <v>25.9</v>
+        <v>23.9</v>
       </c>
       <c r="L52" t="n">
-        <v>39.7</v>
+        <v>48.7</v>
       </c>
       <c r="M52" t="n">
-        <v>43.5</v>
+        <v>47.5</v>
       </c>
       <c r="N52" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="O52" t="n">
+        <v>60</v>
+      </c>
+      <c r="P52" t="n">
         <v>40</v>
       </c>
-      <c r="P52" t="n">
-        <v>55</v>
-      </c>
       <c r="Q52" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="S52" t="n">
-        <v>-3.8</v>
+        <v>1.1</v>
       </c>
       <c r="T52" t="n">
-        <v>-2.2</v>
+        <v>-3.2</v>
       </c>
       <c r="U52" t="n">
         <v>20</v>
       </c>
       <c r="V52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>8.0 (3g)</t>
         </is>
       </c>
       <c r="X52" t="n">
-        <v>9.800000000000001</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4699,79 +4707,79 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
       <c r="E53" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>6.8</v>
+        <v>31.2</v>
       </c>
       <c r="G53" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="N53" t="n">
         <v>12.2</v>
       </c>
-      <c r="H53" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I53" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K53" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="O53" t="n">
+        <v>40</v>
+      </c>
+      <c r="P53" t="n">
         <v>50</v>
       </c>
-      <c r="M53" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O53" t="n">
-        <v>50</v>
-      </c>
-      <c r="P53" t="n">
-        <v>45</v>
-      </c>
       <c r="Q53" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R53" t="n">
-        <v>-6.3</v>
+        <v>6.4</v>
       </c>
       <c r="S53" t="n">
-        <v>-0.3</v>
+        <v>3.5</v>
       </c>
       <c r="T53" t="n">
-        <v>-1.1</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V53" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>13.2 (6g)</t>
+          <t>25.0 (7g)</t>
         </is>
       </c>
       <c r="X53" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4785,75 +4793,75 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="E54" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="F54" t="n">
-        <v>8.800000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="G54" t="n">
-        <v>9.1</v>
+        <v>15.6</v>
       </c>
       <c r="H54" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="I54" t="n">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J54" t="n">
-        <v>20.7</v>
+        <v>31.1</v>
       </c>
       <c r="K54" t="n">
-        <v>23.9</v>
+        <v>32.8</v>
       </c>
       <c r="L54" t="n">
-        <v>48.7</v>
+        <v>58</v>
       </c>
       <c r="M54" t="n">
-        <v>47.5</v>
+        <v>51.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
+        <v>70</v>
+      </c>
+      <c r="P54" t="n">
         <v>60</v>
       </c>
-      <c r="P54" t="n">
-        <v>40</v>
-      </c>
       <c r="Q54" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="T54" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="U54" t="n">
         <v>20</v>
       </c>
       <c r="V54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>8.0 (3g)</t>
+          <t>15.1 (7g)</t>
         </is>
       </c>
       <c r="X54" t="n">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4867,75 +4875,75 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>16.7</v>
       </c>
       <c r="F55" t="n">
-        <v>31.2</v>
+        <v>16.4</v>
       </c>
       <c r="G55" t="n">
-        <v>26.1</v>
+        <v>14.4</v>
       </c>
       <c r="H55" t="n">
-        <v>25.4</v>
+        <v>14.3</v>
       </c>
       <c r="I55" t="n">
-        <v>24.8</v>
+        <v>13.8</v>
       </c>
       <c r="J55" t="n">
-        <v>37.4</v>
+        <v>24.1</v>
       </c>
       <c r="K55" t="n">
-        <v>35.2</v>
+        <v>23.7</v>
       </c>
       <c r="L55" t="n">
-        <v>50.2</v>
+        <v>43.4</v>
       </c>
       <c r="M55" t="n">
-        <v>46.7</v>
+        <v>41.3</v>
       </c>
       <c r="N55" t="n">
-        <v>12.2</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
         <v>40</v>
       </c>
       <c r="P55" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="R55" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="S55" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>25.0 (7g)</t>
+          <t>10.6 (5g)</t>
         </is>
       </c>
       <c r="X55" t="n">
-        <v>7</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4945,41 +4953,41 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>12.5</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G56" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H56" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="I56" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="J56" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="K56" t="n">
-        <v>32.8</v>
+        <v>30.7</v>
       </c>
       <c r="L56" t="n">
-        <v>58</v>
+        <v>51.9</v>
       </c>
       <c r="M56" t="n">
-        <v>51.1</v>
+        <v>47.5</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O56" t="n">
         <v>60</v>
@@ -4988,36 +4996,36 @@
         <v>50</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R56" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="S56" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="T56" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="U56" t="n">
         <v>20</v>
       </c>
       <c r="V56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>15.1 (7g)</t>
+          <t>16.2 (5g)</t>
         </is>
       </c>
       <c r="X56" t="n">
-        <v>8.300000000000001</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,79 +5035,79 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
       <c r="E57" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="F57" t="n">
-        <v>16.4</v>
+        <v>27.2</v>
       </c>
       <c r="G57" t="n">
-        <v>14.4</v>
+        <v>24</v>
       </c>
       <c r="H57" t="n">
-        <v>14.3</v>
+        <v>25.9</v>
       </c>
       <c r="I57" t="n">
-        <v>13.8</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>24.1</v>
+        <v>36.1</v>
       </c>
       <c r="K57" t="n">
-        <v>23.7</v>
+        <v>35.5</v>
       </c>
       <c r="L57" t="n">
-        <v>43.4</v>
+        <v>56.7</v>
       </c>
       <c r="M57" t="n">
-        <v>41.3</v>
+        <v>55</v>
       </c>
       <c r="N57" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="O57" t="n">
         <v>30</v>
       </c>
       <c r="P57" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="R57" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="S57" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="T57" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="U57" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>10.6 (5g)</t>
+          <t>29.2 (6g)</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-7.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5113,75 +5121,75 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>24.7</v>
       </c>
       <c r="F58" t="n">
-        <v>13.2</v>
+        <v>22.4</v>
       </c>
       <c r="G58" t="n">
-        <v>14.3</v>
+        <v>22.8</v>
       </c>
       <c r="H58" t="n">
-        <v>12.6</v>
+        <v>19.5</v>
       </c>
       <c r="I58" t="n">
-        <v>12.7</v>
+        <v>22.2</v>
       </c>
       <c r="J58" t="n">
-        <v>29.7</v>
+        <v>31.8</v>
       </c>
       <c r="K58" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="L58" t="n">
-        <v>51.9</v>
+        <v>43.5</v>
       </c>
       <c r="M58" t="n">
-        <v>47.5</v>
+        <v>43.4</v>
       </c>
       <c r="N58" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O58" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P58" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q58" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.2</v>
       </c>
-      <c r="R58" t="n">
-        <v>0.5</v>
-      </c>
       <c r="S58" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="T58" t="n">
-        <v>-1</v>
+        <v>0.7</v>
       </c>
       <c r="U58" t="n">
         <v>20</v>
       </c>
       <c r="V58" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>16.2 (5g)</t>
+          <t>20.9 (7g)</t>
         </is>
       </c>
       <c r="X58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5191,236 +5199,72 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="E59" t="n">
-        <v>26.7</v>
+        <v>22.7</v>
       </c>
       <c r="F59" t="n">
-        <v>27.2</v>
+        <v>20.8</v>
       </c>
       <c r="G59" t="n">
-        <v>24</v>
+        <v>16.2</v>
       </c>
       <c r="H59" t="n">
-        <v>25.9</v>
+        <v>17.6</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>36.1</v>
+        <v>29.9</v>
       </c>
       <c r="K59" t="n">
-        <v>35.5</v>
+        <v>29.3</v>
       </c>
       <c r="L59" t="n">
-        <v>56.7</v>
+        <v>43.1</v>
       </c>
       <c r="M59" t="n">
-        <v>55</v>
+        <v>45.7</v>
       </c>
       <c r="N59" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="O59" t="n">
         <v>30</v>
       </c>
       <c r="P59" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q59" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="S59" t="n">
-        <v>1.7</v>
+        <v>-2.6</v>
       </c>
       <c r="T59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U59" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="V59" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>29.2 (6g)</t>
+          <t>14.5 (4g)</t>
         </is>
       </c>
       <c r="X59" t="n">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Forward</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H60" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K60" t="n">
-        <v>31</v>
-      </c>
-      <c r="L60" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="M60" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N60" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O60" t="n">
-        <v>30</v>
-      </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U60" t="n">
-        <v>20</v>
-      </c>
-      <c r="V60" t="n">
-        <v>3</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>20.9 (7g)</t>
-        </is>
-      </c>
-      <c r="X60" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G61" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H61" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I61" t="n">
-        <v>17</v>
-      </c>
-      <c r="J61" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="L61" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="N61" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O61" t="n">
-        <v>30</v>
-      </c>
-      <c r="P61" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="R61" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S61" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U61" t="n">
-        <v>11</v>
-      </c>
-      <c r="V61" t="n">
-        <v>3</v>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>14.5 (4g)</t>
-        </is>
-      </c>
-      <c r="X61" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5435,7 +5279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -5516,7 +5360,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5525,29 +5369,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.512</v>
+        <v>0.535</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.826</v>
+        <v>2.85</v>
       </c>
       <c r="K2" t="n">
-        <v>1.909</v>
+        <v>1.4</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Okongwu has a H2H avg of 15.6 pts vs this opponent (+2.1 vs line) — supporting the OVER. His H2H avg of 15.6 pts is 1.5 above his season L30; His TS% shifts +5.3% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 13.8 pts (0.3 pts above line; 51% blended confidence).</t>
+          <t>Okongwu shows low scoring variance (σ=4.7) — highly predictable output. His H2H avg of 15.6 pts is 1.5 above his season L30; His TS% shifts +5.3% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). 8/10 signals agree (Volume, HR L30, Trend, Context among the strongest); HR L10, H2H dissent. Projection model targets 13.6 pts (0.9 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5417,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.575</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5582,27 +5426,27 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="K3" t="n">
-        <v>1.935</v>
+        <v>1.4</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Anunoby's L30 average of 18.5 pts is 3.0 above the 15.5 line, works against the UNDER. His H2H avg of 15.7 pts is 2.8 below his season L30; His TS% shifts -6.3% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#6). Mixed signal picture: 2/10 agree. Agreeing: Trend, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 13.8 pts (1.7 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
+          <t>Anunoby's L30 average of 18.5 pts is 3.0 above the 15.5 line, works against the UNDER. His H2H avg of 15.7 pts is 2.8 below his season L30; His TS% shifts -6.3% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#6). Mixed signal picture: 2/10 agree. Agreeing: Trend, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.3 pts (1.2 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5612,7 +5456,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5621,36 +5465,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.619</v>
+        <v>0.553</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5</v>
+        <v>14.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.855</v>
+        <v>1.357</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Kuminga shows recent scoring down 2.6 pts vs L30 (L5 vs L30 trend). FG% trend -5.5% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#27). 7/10 signals agree (HR L30, HR L10, Trend, Defense among the strongest); Volume, Context dissent. Projection model targets 6.5 pts (4.0 pts below line; 61% blended confidence).</t>
+          <t>Hart has a H2H avg of 16.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His H2H avg of 16.6 pts is 4.4 above his season L30; His TS% shifts +7.9% in this matchup. Opponent ranks as below-average defense (#20) with above-average pace (#6). 6/10 signals agree — Context, Defense, H2H support over; Volume, HR L30 against. Projection model targets 14.3 pts (1.8 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5660,45 +5504,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.515</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>11.4</v>
+        <v>22.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.885</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.847</v>
+        <v>1.345</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Daniels's L30 average of 11.9 pts vs line of 11.5, supports the lean OVER. FG% trend +4.0% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#27). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 11.4 pts (0.1 pts below line; 51% blended confidence).</t>
+          <t>Alexander-Walker has a H2H avg of 16.5 pts vs this opponent (-3.0 vs line) — working against the OVER. His H2H avg of 16.5 pts is 4.6 below his season L30; FG% trend +5.7% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 22.8 pts (3.3 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5708,45 +5552,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.511</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>25.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.833</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.893</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Hart has a H2H avg of 16.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His H2H avg of 16.6 pts is 4.4 above his season L30; His TS% shifts +7.9% in this matchup. Opponent ranks as below-average defense (#20) with above-average pace (#6). 6/10 signals agree — Context, Defense, H2H support over; Volume, HR L30 against. Projection model targets 15.0 pts (2.5 pts above line; 56% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
+          <t>Brunson's L30 average of 23.2 pts vs line of 25.5, supports the UNDER. His H2H avg of 27.2 pts is 4.0 above his season L30. Opponent ranks as below-average defense (#20) with above-average pace (#6). Mixed signal picture: 3/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 25.1 pts (0.4 pts below line; 51% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5756,45 +5600,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.609</v>
+        <v>0.694</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1.909</v>
+        <v>1.87</v>
       </c>
       <c r="K7" t="n">
-        <v>1.826</v>
+        <v>1.87</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Risacher has a H2H avg of 13.2 pts vs this opponent (+7.7 vs line) — supporting the OVER. His H2H avg of 13.2 pts is 4.5 above his season L30; His TS% shifts +3.1% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 8.8 pts (3.3 pts above line; 60% blended confidence). Risk: minutes trending down (16.8 L10 vs 20.7 L30 — role reduction would suppress counting stats.</t>
+          <t>McCollum has a H2H avg of 10.3 pts vs this opponent (-7.2 vs line) — supporting the UNDER. His H2H avg of 10.3 pts is 8.5 below his season L30; His TS% shifts -15.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#27). Mixed signal picture: 4/10 agree. Agreeing: Trend, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.6 pts (7.9 pts below line; 69% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5804,45 +5648,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.528</v>
+        <v>0.608</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.769</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.98</v>
+        <v>1.357</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Brunson's L30 average of 23.2 pts vs line of 25.5, supports the UNDER. His H2H avg of 27.2 pts is 4.0 above his season L30. Opponent ranks as below-average defense (#20) with above-average pace (#6). Mixed signal picture: 3/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 24.4 pts (1.1 pts below line; 52% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
+          <t>Towns has a H2H avg of 29.3 pts vs this opponent (+9.8 vs line) — supporting the OVER. His H2H avg of 29.3 pts is 9.9 above his season L30; His TS% shifts +3.6% in this matchup. Opponent ranks as below-average defense (#17) with above-average pace (#6). 6/10 signals agree — HR L30, HR L10, Context support over; Volume, Trend against. Projection model targets 23.2 pts (3.7 pts above line; 60% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5852,45 +5696,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.64</v>
+        <v>0.524</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>23.1</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.909</v>
+        <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>1.826</v>
+        <v>1.4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Alexander-Walker shows recent scoring up 2.3 pts vs L30 (L5 vs L30 trend). His H2H avg of 16.5 pts is 4.6 below his season L30; FG% trend +5.7% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 23.1 pts (4.6 pts above line; 63% blended confidence).</t>
+          <t>Shamet shows recent scoring down 3.0 pts vs L30 (L5 vs L30 trend). His H2H avg of 6.3 pts is 3.9 below his season L30; FG% trend -4.5% (L10 vs L30). Opponent ranks as below-average defense (#20) with above-average pace (#6). Mixed signal picture: 3/10 agree. Agreeing: Trend, H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.8 pts (0.7 pts below line; 52% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5905,40 +5749,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.679</v>
+        <v>0.632</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>10.3</v>
+        <v>5.9</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.87</v>
+        <v>1.417</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>McCollum has a H2H avg of 10.3 pts vs this opponent (-7.2 vs line) — supporting the UNDER. His H2H avg of 10.3 pts is 8.5 below his season L30; His TS% shifts -15.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#27). Mixed signal picture: 4/10 agree. Agreeing: Trend, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 10.3 pts (7.2 pts below line; 67% blended confidence).</t>
+          <t>Kuminga shows recent scoring down 2.6 pts vs L30 (L5 vs L30 trend). FG% trend -5.5% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#27). 7/10 signals agree (HR L30, HR L10, Trend, Defense among the strongest); Volume, Context dissent. Projection model targets 5.9 pts (4.6 pts below line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5948,45 +5792,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.614</v>
+        <v>0.516</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>18.4</v>
+        <v>11.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.971</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.769</v>
+        <v>1.364</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Johnson has a H2H avg of 18.6 pts vs this opponent (-3.9 vs line) — supporting the UNDER. His H2H avg of 18.6 pts is 3.7 below his season L30; His TS% shifts -5.7% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). 7/10 signals agree (Volume, HR L30, Trend, Context among the strongest); HR L10, FG Trend dissent. Projection model targets 18.4 pts (4.1 pts below line; 61% blended confidence).</t>
+          <t>[Low conviction — lean only] Daniels's L30 average of 11.9 pts vs line of 11.5, supports the lean OVER. FG% trend +4.0% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#27). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 11.6 pts (0.1 pts above line; 51% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5996,45 +5840,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.52</v>
+        <v>0.604</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>13.1</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.909</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>1.826</v>
+        <v>1.333</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Bridges has a H2H avg of 16.9 pts vs this opponent (+3.4 vs line) — working against the UNDER. His H2H avg of 16.9 pts is 4.2 above his season L30. Opponent ranks as below-average defense (#20) with above-average pace (#6). Mixed signal picture: 3/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 13.1 pts (0.4 pts below line; 52% blended confidence).</t>
+          <t>Risacher has a H2H avg of 13.2 pts vs this opponent (+7.7 vs line) — supporting the OVER. His H2H avg of 13.2 pts is 4.5 above his season L30; His TS% shifts +3.1% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 8.6 pts (3.1 pts above line; 60% blended confidence). Risk: minutes trending down (16.8 L10 vs 20.7 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6044,7 +5888,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6053,7 +5897,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.642</v>
+        <v>0.579</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
@@ -6062,27 +5906,27 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>18.5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.926</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>1.82</v>
+        <v>1.357</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Towns has a H2H avg of 29.3 pts vs this opponent (+9.8 vs line) — supporting the OVER. His H2H avg of 29.3 pts is 9.9 above his season L30; His TS% shifts +3.6% in this matchup. Opponent ranks as below-average defense (#17) with above-average pace (#6). 6/10 signals agree — HR L30, HR L10, Context support over; Volume, Trend against. Projection model targets 24.6 pts (5.1 pts above line; 64% blended confidence).</t>
+          <t>Johnson has a H2H avg of 18.6 pts vs this opponent (-2.9 vs line) — supporting the UNDER. His H2H avg of 18.6 pts is 3.7 below his season L30; His TS% shifts -5.7% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#27). 6/10 signals agree — HR L30, Trend, Context support under; Volume, HR L10 against. Projection model targets 18.5 pts (3.0 pts below line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6092,45 +5936,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>0.521</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>12.6</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1.909</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.826</v>
+        <v>1.408</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Shamet shows recent scoring down 3.0 pts vs L30 (L5 vs L30 trend). His H2H avg of 6.3 pts is 3.9 below his season L30; FG% trend -4.5% (L10 vs L30). Opponent ranks as below-average defense (#20) with above-average pace (#6). Mixed signal picture: 3/10 agree. Agreeing: Trend, H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.0 pts (0.5 pts below line; 52% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>[Low conviction — lean only] Bridges has a H2H avg of 16.9 pts vs this opponent (+4.4 vs line) — supporting the lean OVER. His H2H avg of 16.9 pts is 4.2 above his season L30. Opponent ranks as below-average defense (#20) with above-average pace (#6). 8/10 signals agree (Volume, Trend, Context, Defense among the strongest); HR L30, HR L10 dissent. Projection model targets 12.6 pts (0.1 pts above line; 52% blended confidence). Risk: only 40% hit rate over L30 — line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6149,36 +5993,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.523</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>13.2</v>
+        <v>19.7</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
-        <v>1.769</v>
+        <v>1.833</v>
       </c>
       <c r="K15" t="n">
-        <v>1.971</v>
+        <v>1.909</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Harris's L30 average of 12.8 pts vs line of 13.5, supports the UNDER. His H2H avg of 15.2 pts is 2.4 above his season L30; His TS% shifts +5.3% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, FG Trend dissent. Projection model targets 13.2 pts (0.3 pts below line; 52% blended confidence).</t>
+          <t>Banchero shows recent scoring down 8.4 pts vs L30 (L5 vs L30 trend). His H2H avg of 26.7 pts is 3.9 above his season L30; FG% trend -4.0% (L10 vs L30). Opponent ranks as average defense (#14) with moderate pace (#20). 7/10 signals agree (HR L10, Trend, Context, Defense among the strongest); Volume, HR L30 dissent. Projection model targets 19.7 pts (2.8 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=10.7) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6188,7 +6032,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6197,36 +6041,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.541</v>
+        <v>0.594</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>12.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.758</v>
+        <v>1.909</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Thompson shows low scoring variance (σ=4.1) — highly predictable output. His H2H avg of 10.2 pts is 1.6 above his season L30; His TS% shifts -5.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 8.1 pts (1.4 pts below line; 54% blended confidence).</t>
+          <t>Silva's L30 average of 11.3 pts vs line of 9.5, supports the OVER. His H2H avg of 9.2 pts is 2.1 below his season L30; His TS% shifts +10.5% in this matchup. Opponent ranks as average defense (#14) with moderate pace (#20). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 12.7 pts (3.2 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6236,45 +6080,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>21</v>
+        <v>11.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="K17" t="n">
-        <v>1.926</v>
+        <v>1.769</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Banchero has a H2H avg of 26.7 pts vs this opponent (+6.2 vs line) — supporting the OVER. His H2H avg of 26.7 pts is 4.0 above his season L30. Opponent ranks as average defense (#14) with moderate pace (#20). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 21.0 pts (0.5 pts above line; 50% blended confidence). Risk: L3 has dropped to 13.3 (9.4 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>[Low conviction — lean only] Jr. shows recent scoring up 2.8 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.2 pts is 2.8 below his season L30; FG% trend +3.5% (L10 vs L30). Opponent ranks as elite defense (#5) with moderate pace (#20). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, H2H dissent. Projection model targets 11.6 pts (0.1 pts above line; 50% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6284,45 +6128,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.632</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>13.8</v>
+        <v>8.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.962</v>
+        <v>1.769</v>
       </c>
       <c r="K18" t="n">
-        <v>1.775</v>
+        <v>1.952</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Silva shows recent scoring up 2.0 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.2 pts is 2.2 below his season L30; His TS% shifts +10.3% in this matchup. Opponent ranks as average defense (#14) with moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 13.8 pts (4.3 pts above line; 63% blended confidence).</t>
+          <t>Suggs has a H2H avg of 11.7 pts vs this opponent (-2.8 vs line) — supporting the UNDER. His TS% shifts -9.9% in this matchup. Opponent ranks as elite defense (#4) with moderate pace (#20). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, FG Trend dissent. Projection model targets 8.1 pts (6.4 pts below line; 69% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6332,45 +6176,45 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.503</v>
+        <v>0.588</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>11.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.775</v>
+        <v>2.75</v>
       </c>
       <c r="K19" t="n">
-        <v>1.952</v>
+        <v>1.417</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Jr. has a H2H avg of 9.2 pts vs this opponent (-2.3 vs line) — supporting the lean UNDER. His H2H avg of 9.2 pts is 2.7 below his season L30. Opponent ranks as elite defense (#5) with moderate pace (#20). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 11.6 pts (0.1 pts above line; 50% blended confidence). Risk: L3 has surged to 19.0 after a 15-pt performance (7.1 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Carter has a H2H avg of 4.2 pts vs this opponent (-3.3 vs line) — supporting the UNDER. His H2H avg of 4.2 pts is 2.8 below his season L30; FG% trend +4.3% (L10 vs L30). Opponent ranks as elite defense (#4) with moderate pace (#20). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); FG Trend, Min Trend dissent. Projection model targets 4.7 pts (2.8 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6380,45 +6224,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.674</v>
+        <v>0.576</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8.699999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.855</v>
+        <v>1.909</v>
       </c>
       <c r="K20" t="n">
-        <v>1.877</v>
+        <v>1.833</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Suggs has a H2H avg of 11.7 pts vs this opponent (-2.8 vs line) — supporting the UNDER. His TS% shifts -10.2% in this matchup. Opponent ranks as elite defense (#4) with moderate pace (#20). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, FG Trend dissent. Projection model targets 8.7 pts (5.8 pts below line; 67% blended confidence).</t>
+          <t>Bane's L30 average of 22.1 pts vs line of 19.5, supports the OVER. His TS% shifts -3.5% in this matchup; FG% trend -6.5% (L10 vs L30). Opponent ranks as elite defense (#4) with moderate pace (#20). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 22.5 pts (3.0 pts above line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6437,36 +6281,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.521</v>
+        <v>0.582</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>19.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1.87</v>
+        <v>1.952</v>
       </c>
       <c r="K21" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Huerter shows recent scoring up 2.4 pts vs L30 (L5 vs L30 trend). His H2H avg of 11.0 pts is 2.8 above his season L30; His TS% shifts +5.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 9.0 pts (0.5 pts below line; 52% blended confidence).</t>
+          <t>Duren has a H2H avg of 14.7 pts vs this opponent (-7.8 vs line) — supporting the UNDER. His H2H avg of 14.7 pts is 6.8 below his season L30. Opponent ranks as average defense (#11) with slow pace (#29). 5/10 signals agree — Volume, Context, Defense support under; HR L30, HR L10 against. Projection model targets 19.7 pts (2.8 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.6) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6485,36 +6329,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.58</v>
+        <v>0.756</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
-        <v>1.962</v>
+        <v>1.741</v>
       </c>
       <c r="K22" t="n">
-        <v>1.775</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Reed has a H2H avg of 2.2 pts vs this opponent (-7.3 vs line) — supporting the UNDER. His H2H avg of 2.2 pts is 7.0 below his season L30; His TS% shifts +21.9% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 6.6 pts (2.9 pts below line; 58% blended confidence).</t>
+          <t>Jenkins has a H2H avg of 0.7 pts vs this opponent (-16.8 vs line) — supporting the UNDER. His H2H avg of 0.7 pts is 10.9 below his season L30; His TS% shifts -38.4% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 3.5 pts (14.0 pts below line; 75% blended confidence). Risk: L3 has surged to 21.0 after a 8-pt performance (9.4 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6533,36 +6377,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.574</v>
+        <v>0.538</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>1.833</v>
       </c>
       <c r="K23" t="n">
-        <v>1.893</v>
+        <v>1.909</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Duren has a H2H avg of 14.7 pts vs this opponent (-7.8 vs line) — supporting the UNDER. His H2H avg of 14.7 pts is 6.8 below his season L30. Opponent ranks as average defense (#11) with slow pace (#29). 5/10 signals agree — Volume, Context, Defense support under; HR L30, HR L10 against. Projection model targets 20.0 pts (2.5 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.6) introduces outcome uncertainty.</t>
+          <t>Thompson shows low scoring variance (σ=4.1) — highly predictable output. His H2H avg of 10.2 pts is 1.6 above his season L30; His TS% shifts -5.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 8.3 pts (1.2 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6572,7 +6416,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6581,36 +6425,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.74</v>
+        <v>0.593</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>19.9</v>
+        <v>7.3</v>
       </c>
       <c r="I24" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
-        <v>1.826</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Wagner has a H2H avg of 26.2 pts vs this opponent (+14.7 vs line) — supporting the OVER. His H2H avg of 26.2 pts is 5.3 above his season L30. Opponent ranks as average defense (#14) with moderate pace (#20). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 19.9 pts (8.4 pts above line; 73% blended confidence). Risk: L3 has dropped to 11.7 (9.2 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Robinson has a H2H avg of 7.9 pts vs this opponent (-2.6 vs line) — supporting the UNDER. His H2H avg of 7.9 pts is 4.4 below his season L30; His TS% shifts -10.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.3 pts (3.2 pts below line; 59% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6629,36 +6473,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.756</v>
+        <v>0.575</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>12.6</v>
       </c>
       <c r="I25" t="n">
-        <v>15.5</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="K25" t="n">
-        <v>1.943</v>
+        <v>1.909</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Jenkins has a H2H avg of 0.7 pts vs this opponent (-17.8 vs line) — supporting the UNDER. His H2H avg of 0.7 pts is 10.9 below his season L30; His TS% shifts -38.4% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 3.0 pts (15.5 pts below line; 75% blended confidence). Risk: L3 has surged to 21.0 after a 8-pt performance (9.4 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Harris's L30 average of 12.8 pts vs line of 14.5, supports the UNDER. His H2H avg of 15.2 pts is 2.4 above his season L30; His TS% shifts +5.3% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, FG Trend dissent. Projection model targets 12.6 pts (1.9 pts below line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6677,36 +6521,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.588</v>
+        <v>0.57</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.787</v>
+        <v>2.05</v>
       </c>
       <c r="K26" t="n">
-        <v>1.943</v>
+        <v>1.73</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Robinson has a H2H avg of 7.9 pts vs this opponent (-2.6 vs line) — supporting the UNDER. His H2H avg of 7.9 pts is 4.4 below his season L30; His TS% shifts -10.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.5 pts (3.0 pts below line; 58% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Reed has a H2H avg of 2.2 pts vs this opponent (-6.3 vs line) — supporting the UNDER. His H2H avg of 2.2 pts is 7.0 below his season L30; His TS% shifts +21.9% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 5/10 signals agree — HR L30, Context, Defense support under; Volume, HR L10 against. Projection model targets 5.7 pts (2.8 pts below line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6721,40 +6565,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.608</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.847</v>
+        <v>1.971</v>
       </c>
       <c r="K27" t="n">
-        <v>1.877</v>
+        <v>1.746</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Carter has a H2H avg of 4.2 pts vs this opponent (-3.3 vs line) — supporting the UNDER. His H2H avg of 4.2 pts is 2.5 below his season L30. Opponent ranks as elite defense (#4) with moderate pace (#20). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); FG Trend, Min Trend dissent. Projection model targets 4.1 pts (3.4 pts below line; 60% blended confidence).</t>
+          <t>Huerter shows recent scoring up 2.4 pts vs L30 (L5 vs L30 trend). His H2H avg of 11.0 pts is 2.8 above his season L30; His TS% shifts +5.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 8.1 pts (2.4 pts below line; 55% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6773,29 +6617,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.61</v>
+        <v>0.739</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>21.6</v>
+        <v>17.9</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1.746</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.357</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Bane's L30 average of 22.0 pts is 4.5 above the 17.5 line, supports the OVER. His TS% shifts -3.5% in this matchup; FG% trend -5.8% (L10 vs L30). Opponent ranks as elite defense (#4) with moderate pace (#20). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 21.6 pts (4.1 pts above line; 61% blended confidence).</t>
+          <t>Wagner has a H2H avg of 26.2 pts vs this opponent (+16.7 vs line) — supporting the OVER. His H2H avg of 26.2 pts is 5.8 above his season L30. Opponent ranks as average defense (#14) with moderate pace (#20). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 17.9 pts (8.4 pts above line; 73% blended confidence). Risk: L3 has dropped to 13.7 (6.7 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6665,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.538</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -6830,20 +6674,20 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1.926</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.806</v>
+        <v>1.408</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Mobley has a H2H avg of 23.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 23.0 pts is 4.5 above his season L30; FG% trend +4.5% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 21.4 pts (1.9 pts above line; 53% blended confidence). Risk: high scoring volatility (σ=8.8) introduces outcome uncertainty.</t>
+          <t>Mobley has a H2H avg of 23.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 23.0 pts is 4.5 above his season L30; FG% trend +4.5% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 22.2 pts (2.7 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=8.8) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -6869,29 +6713,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.542</v>
+        <v>0.545</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Harden shows recent scoring down 4.3 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). Mixed signal picture: 3/10 agree. Agreeing: HR L30, HR L10, Trend. Counter-signals: Volume, Context, Defense. Projection model targets 17.9 pts (1.6 pts below line; 54% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
+          <t>Harden shows recent scoring down 2.2 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). Mixed signal picture: 1/10 agree. Agreeing: Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 18.3 pts (1.2 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6761,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -6926,20 +6770,20 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1.826</v>
+        <v>2.7</v>
       </c>
       <c r="K31" t="n">
-        <v>1.909</v>
+        <v>1.435</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Allen's L30 average of 16.6 pts vs line of 14.5, supports the OVER. His H2H avg of 15.0 pts is 1.6 below his season L30; FG% trend +3.8% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Min Trend dissent. Projection model targets 15.6 pts (1.1 pts above line; 56% blended confidence).</t>
+          <t>Allen's L30 average of 16.6 pts vs line of 14.5, supports the OVER. His H2H avg of 15.0 pts is 1.6 below his season L30; FG% trend +3.8% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Min Trend dissent. Projection model targets 15.4 pts (0.9 pts above line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6800,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6965,7 +6809,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.518</v>
+        <v>0.53</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -6974,20 +6818,20 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>12.2</v>
+        <v>10.1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.826</v>
+        <v>1.87</v>
       </c>
       <c r="K32" t="n">
-        <v>1.909</v>
+        <v>1.855</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Strus shows recent scoring up 4.6 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). 5/10 signals agree — Trend, Context, Defense support over; Volume, HR L30 against. Projection model targets 12.2 pts (0.7 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=9.6) introduces outcome uncertainty.</t>
+          <t>Strus shows recent scoring up 4.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 10.1 pts (1.4 pts below line; 53% blended confidence). Risk: high scoring volatility (σ=10.0) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -7013,41 +6857,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.519</v>
+        <v>0.53</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>26.5</v>
+        <v>27.1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
-        <v>1.926</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>1.806</v>
+        <v>1.364</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Mitchell shows recent scoring down 4.6 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). 5/10 signals agree — Context, Defense, Pace support over; Volume, HR L30 against. Projection model targets 26.5 pts (1.0 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=10.5) introduces outcome uncertainty.</t>
+          <t>Mitchell shows recent scoring down 3.4 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with above-average pace (#7). 6/10 signals agree — Volume, HR L10, Context support over; HR L30, Trend against. Projection model targets 27.1 pts (1.6 pts above line; 53% blended confidence). Risk: high scoring volatility (σ=11.4) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7061,41 +6905,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.724</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>1.758</v>
+        <v>2.9</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>1.385</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Jackson's L30 average of 16.5 pts vs line of 14.5, works against the UNDER. Opponent ranks as below-average defense (#16) with above-average pace (#10). Mixed signal picture: 1/10 agree. Agreeing: FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 6.5 pts (8.0 pts below line; 72% blended confidence). Risk: L3 has surged to 21.3 after a 28-pt performance (4.8 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Jr.'s L30 average of 14.5 pts is 4.0 above the 10.5 line, works against the UNDER. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.5 pts (2.0 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=9.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7109,36 +6953,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.608</v>
+        <v>0.546</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>9.1</v>
+        <v>16.9</v>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K35" t="n">
-        <v>1.82</v>
+        <v>1.385</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Coward shows low scoring variance (σ=5.0) — highly predictable output. Opponent ranks as average defense (#12) with above-average pace (#10). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 9.1 pts (4.4 pts below line; 60% blended confidence).</t>
+          <t>Castle shows recent scoring up 3.1 pts vs L30 (L5 vs L30 trend). His TS% shifts +11.2% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 16.9 pts (1.6 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7148,7 +6992,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7157,19 +7001,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.548</v>
+        <v>0.731</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>1.87</v>
@@ -7179,14 +7023,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>George shows recent scoring up 7.2 pts vs L30 (L5 vs L30 trend). FG% trend +3.2% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Defense dissent. Projection model targets 19.0 pts (1.5 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=9.5) introduces outcome uncertainty.</t>
+          <t>Edgecombe's L30 average of 16.9 pts is 4.4 above the 12.5 line, works against the UNDER. FG% trend +6.3% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 4.4 pts (8.1 pts below line; 73% blended confidence). Risk: high scoring volatility (σ=10.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7205,7 +7049,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -7214,27 +7058,27 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9.6</v>
+        <v>24.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="K37" t="n">
-        <v>1.935</v>
+        <v>1.4</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 average of 14.5 pts is 4.0 above the 10.5 line, works against the UNDER. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.6 pts (0.9 pts below line; 53% blended confidence). Risk: high scoring volatility (σ=9.3) introduces outcome uncertainty.</t>
+          <t>Maxey shows low scoring variance (σ=4.1) — highly predictable output. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Context, Defense. Counter-signals: Volume, HR L30, HR L10. Projection model targets 24.8 pts (0.7 pts below line; 52% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7244,45 +7088,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
-        <v>1.787</v>
+        <v>2.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1.952</v>
+        <v>1.417</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Champagnie shows recent scoring up 3.1 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.5% in this matchup. Opponent ranks as below-average defense (#21) with slow pace (#23). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Pace dissent. Projection model targets 12.0 pts (1.5 pts above line; 56% blended confidence).</t>
+          <t>Fox has a H2H avg of 21.7 pts vs this opponent (+6.2 vs line) — working against the UNDER. His H2H avg of 21.7 pts is 5.4 above his season L30; His TS% shifts +15.1% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — HR L10, Trend, Context support under; Volume, HR L30 against. Projection model targets 13.8 pts (1.7 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7301,36 +7145,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.528</v>
+        <v>0.585</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>17.6</v>
+        <v>2.9</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
-        <v>1.952</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>1.787</v>
+        <v>1.364</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Castle shows recent scoring up 3.1 pts vs L30 (L5 vs L30 trend). His TS% shifts +11.2% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 17.6 pts (0.9 pts below line; 52% blended confidence).</t>
+          <t>Barlow shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). FG% trend +6.7% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 2.9 pts (2.6 pts below line; 58% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7340,7 +7184,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -7349,7 +7193,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.524</v>
+        <v>0.742</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -7358,27 +7202,27 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="J40" t="n">
-        <v>1.962</v>
+        <v>2.85</v>
       </c>
       <c r="K40" t="n">
-        <v>1.775</v>
+        <v>1.4</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Vassell has a H2H avg of 19.0 pts vs this opponent (+5.5 vs line) — supporting the OVER. His H2H avg of 19.0 pts is 5.9 above his season L30; His TS% shifts +12.7% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 5/10 signals agree — HR L30, Context, Defense support over; Volume, HR L10 against. Projection model targets 14.3 pts (0.8 pts above line; 52% blended confidence).</t>
+          <t>Wembanyama shows recent scoring up 6.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#21) with slow pace (#23). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 17.9 pts (10.6 pts below line; 74% blended confidence). Risk: L3 has surged to 38.7 after a 21-pt performance (13.1 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7397,36 +7241,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.713</v>
+        <v>0.544</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>5.1</v>
+        <v>11.1</v>
       </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
-        <v>1.746</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>2.01</v>
+        <v>1.357</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Edgecombe's L30 average of 16.9 pts is 4.4 above the 12.5 line, works against the UNDER. FG% trend +6.3% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 5.1 pts (7.4 pts below line; 71% blended confidence). Risk: high scoring volatility (σ=10.2) introduces outcome uncertainty.</t>
+          <t>Johnson's L30 average of 12.3 pts vs line of 12.5, supports the UNDER. Opponent ranks as below-average defense (#21) with slow pace (#23). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 11.1 pts (1.4 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7436,45 +7280,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.529</v>
+        <v>0.739</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>24.4</v>
+        <v>20.2</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>1.82</v>
+        <v>2.85</v>
       </c>
       <c r="K42" t="n">
-        <v>1.917</v>
+        <v>1.4</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Maxey shows low scoring variance (σ=4.1) — highly predictable output. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Context, Defense. Counter-signals: Volume, HR L30, HR L10. Projection model targets 24.4 pts (1.1 pts below line; 52% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Harper's L30 average of 13.3 pts vs line of 11.5, supports the OVER. Opponent ranks as below-average defense (#16) with slow pace (#23). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Pace dissent. Projection model targets 20.2 pts (8.7 pts above line; 73% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7484,7 +7328,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7493,36 +7337,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.552</v>
+        <v>0.555</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>13.6</v>
+        <v>19.3</v>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
-        <v>1.787</v>
+        <v>2.85</v>
       </c>
       <c r="K43" t="n">
-        <v>1.952</v>
+        <v>1.4</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Fox has a H2H avg of 21.7 pts vs this opponent (+6.2 vs line) — working against the UNDER. His H2H avg of 21.7 pts is 5.4 above his season L30; His TS% shifts +15.1% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — HR L10, Trend, Context support under; Volume, HR L30 against. Projection model targets 13.6 pts (1.9 pts below line; 55% blended confidence).</t>
+          <t>George shows recent scoring up 7.2 pts vs L30 (L5 vs L30 trend). FG% trend +3.2% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Defense dissent. Projection model targets 19.3 pts (1.8 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=9.5) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7532,7 +7376,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7541,36 +7385,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.586</v>
+        <v>0.542</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.8</v>
+        <v>11.1</v>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
-        <v>1.714</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>2.05</v>
+        <v>1.345</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Barlow shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). FG% trend +6.7% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 2.8 pts (2.7 pts below line; 58% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Champagnie shows recent scoring up 3.1 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.5% in this matchup. Opponent ranks as below-average defense (#21) with slow pace (#23). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Pace dissent. Projection model targets 11.1 pts (0.6 pts above line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7580,7 +7424,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7589,36 +7433,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.747</v>
+        <v>0.516</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
-        <v>1.935</v>
+        <v>3.1</v>
       </c>
       <c r="K45" t="n">
-        <v>1.806</v>
+        <v>1.345</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Embiid's L30 average of 28.4 pts vs line of 28.5, supports the UNDER. Opponent ranks as below-average defense (#18) with above-average pace (#9). Mixed signal picture: 4/10 agree. Agreeing: Volume, Trend, Context. Counter-signals: HR L30, HR L10, Defense. Projection model targets 14.2 pts (14.3 pts below line; 74% blended confidence).</t>
+          <t>Vassell has a H2H avg of 19.0 pts vs this opponent (+5.5 vs line) — supporting the OVER. His H2H avg of 19.0 pts is 5.9 above his season L30; His TS% shifts +12.7% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 5/10 signals agree — HR L30, Context, Defense support over; Volume, HR L10 against. Projection model targets 13.9 pts (0.4 pts above line; 51% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7637,41 +7481,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.668</v>
+        <v>0.755</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>21.6</v>
+        <v>10.5</v>
       </c>
       <c r="I46" t="n">
-        <v>6.9</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>1.901</v>
+        <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>1.833</v>
+        <v>1.385</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Wembanyama shows recent scoring up 6.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#21) with slow pace (#23). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 21.6 pts (6.9 pts below line; 66% blended confidence). Risk: L3 has surged to 38.7 after a 21-pt performance (13.1 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Embiid's L30 average of 28.4 pts vs line of 27.5, works against the UNDER. Opponent ranks as below-average defense (#18) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Context, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 10.5 pts (17.0 pts below line; 75% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7685,84 +7529,84 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.536</v>
+        <v>0.6</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
-        <v>1.909</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>1.826</v>
+        <v>1.364</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Johnson's L30 average of 12.3 pts vs line of 12.5, supports the UNDER. Opponent ranks as below-average defense (#21) with slow pace (#23). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 11.4 pts (1.1 pts below line; 53% blended confidence).</t>
+          <t>Gordon has a H2H avg of 12.0 pts vs this opponent (-3.5 vs line) — supporting the UNDER. His H2H avg of 12.0 pts is 3.6 below his season L30. Opponent ranks as below-average defense (#20) with moderate pace (#17). 5/10 signals agree — Trend, Context, H2H support under; Volume, HR L30 against. Projection model targets 11.6 pts (3.9 pts below line; 59% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.679</v>
+        <v>0.587</v>
       </c>
       <c r="F48" t="n">
         <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>19.2</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1.769</v>
+        <v>2.65</v>
       </c>
       <c r="K48" t="n">
-        <v>1.971</v>
+        <v>1.455</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 13.3 pts vs line of 12.5, supports the OVER. Opponent ranks as below-average defense (#16) with slow pace (#23). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Pace dissent. Projection model targets 19.2 pts (6.7 pts above line; 67% blended confidence).</t>
+          <t>III shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). His H2H avg of 5.5 pts is 2.0 below his season L30; His TS% shifts +3.5% in this matchup. Opponent ranks as strong defense (#10) with fast pace (#3). 7/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, Pace dissent. Projection model targets 5.0 pts (2.5 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7781,36 +7625,36 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.574</v>
+        <v>0.527</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1.758</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>1.98</v>
+        <v>1.364</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Gordon has a H2H avg of 12.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 12.0 pts is 3.6 below his season L30. Opponent ranks as below-average defense (#20) with moderate pace (#18). Mixed signal picture: 4/10 agree. Agreeing: Trend, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 11.7 pts (2.8 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
+          <t>Camara shows recent scoring up 2.9 pts vs L30 (L5 vs L30 trend). FG% trend +11.2% (L10 vs L30). Opponent ranks as below-average defense (#20) with fast pace (#3). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 13.5 pts (1.0 pts below line; 52% blended confidence). Risk: L3 has surged to 21.0 after a 11-pt performance (7.7 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7820,7 +7664,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7829,36 +7673,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.586</v>
+        <v>0.587</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
-        <v>1.943</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
-        <v>1.8</v>
+        <v>1.345</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>III shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). His H2H avg of 5.5 pts is 2.0 below his season L30; His TS% shifts +3.5% in this matchup. Opponent ranks as strong defense (#10) with fast pace (#3). 7/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, Pace dissent. Projection model targets 5.0 pts (2.5 pts below line; 58% blended confidence).</t>
+          <t>Jr. has a H2H avg of 15.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 15.0 pts is 1.9 above his season L30; His TS% shifts +9.8% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 15.0 pts (3.5 pts above line; 58% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7868,7 +7712,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7877,36 +7721,36 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.545</v>
+        <v>0.577</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>13.4</v>
+        <v>15.9</v>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
-        <v>1.893</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>1.833</v>
+        <v>1.364</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Camara has a H2H avg of 12.7 pts vs this opponent (-2.8 vs line) — supporting the UNDER. FG% trend +11.2% (L10 vs L30). Opponent ranks as below-average defense (#20) with fast pace (#3). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 13.4 pts (2.1 pts below line; 54% blended confidence). Risk: L3 has surged to 21.0 after a 11-pt performance (7.7 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Clingan shows recent scoring down 6.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +9.1% in this matchup. Opponent ranks as strong defense (#10) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 15.9 pts (3.4 pts above line; 57% blended confidence). Risk: L3 has dropped to 4.7 (8.4 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7925,36 +7769,36 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.588</v>
+        <v>0.545</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>9.1</v>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1.855</v>
+        <v>2.8</v>
       </c>
       <c r="K52" t="n">
-        <v>1.877</v>
+        <v>1.408</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Jr. has a H2H avg of 15.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. His H2H avg of 15.0 pts is 1.9 above his season L30; His TS% shifts +9.8% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 15.0 pts (3.5 pts above line; 58% blended confidence). Risk: high scoring volatility (σ=7.1) introduces outcome uncertainty.</t>
+          <t>Brown shows low scoring variance (σ=4.3) — highly predictable output. His TS% shifts +13.9% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#17). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Pace dissent. Projection model targets 9.1 pts (1.6 pts above line; 54% blended confidence). Risk: only 40% hit rate over L30 — line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7964,45 +7808,45 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.519</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>15.4</v>
+        <v>24.2</v>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
-        <v>1.826</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>1.909</v>
+        <v>1.357</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Clingan shows recent scoring down 6.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +9.1% in this matchup. Opponent ranks as strong defense (#10) with fast pace (#3). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 15.4 pts (2.9 pts above line; 56% blended confidence). Risk: L3 has dropped to 4.7 (8.4 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>[Low conviction — lean only] Murray shows recent scoring up 6.4 pts vs L30 (L5 vs L30 trend). His TS% shifts +7.0% in this matchup; FG% trend +3.5% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#17). 7/10 signals agree (Volume, Trend, Context, Defense among the strongest); HR L30, HR L10 dissent. Projection model targets 24.2 pts (0.3 pts below line; 51% blended confidence). Risk: high scoring volatility (σ=12.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8017,40 +7861,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.538</v>
+        <v>0.577</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>8.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.926</v>
+        <v>1.8</v>
       </c>
       <c r="K54" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Brown shows low scoring variance (σ=4.3) — highly predictable output. His TS% shifts +13.9% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Pace dissent. Projection model targets 8.8 pts (1.3 pts above line; 53% blended confidence). Risk: only 40% hit rate over L30 — line may be set fairly.</t>
+          <t>Braun has a H2H avg of 15.1 pts vs this opponent (+3.6 vs line) — supporting the OVER. His H2H avg of 15.1 pts is 2.6 above his season L30; His TS% shifts +8.3% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#17). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Pace, Min Trend dissent. Projection model targets 13.3 pts (1.8 pts above line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8060,45 +7904,45 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.529</v>
+        <v>0.587</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>25.2</v>
+        <v>11.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
-        <v>1.775</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>1.962</v>
+        <v>1.364</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Murray shows recent scoring up 6.4 pts vs L30 (L5 vs L30 trend). His TS% shifts +7.0% in this matchup; FG% trend +3.5% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#18). 7/10 signals agree (Volume, Trend, Context, Defense among the strongest); HR L30, HR L10 dissent. Projection model targets 25.2 pts (0.7 pts above line; 52% blended confidence). Risk: high scoring volatility (σ=12.2) introduces outcome uncertainty.</t>
+          <t>Henderson has a H2H avg of 10.6 pts vs this opponent (-3.9 vs line) — supporting the UNDER. His H2H avg of 10.6 pts is 3.2 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Pace against. Projection model targets 11.2 pts (3.3 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8117,36 +7961,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.548</v>
+        <v>0.541</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1.769</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>1.364</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Braun has a H2H avg of 15.1 pts vs this opponent (+2.6 vs line) — supporting the OVER. His H2H avg of 15.1 pts is 2.6 above his season L30; His TS% shifts +8.3% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). 6/10 signals agree — HR L10, Trend, Context support over; Volume, HR L30 against. Projection model targets 13.7 pts (1.2 pts above line; 54% blended confidence).</t>
+          <t>Johnson has a H2H avg of 16.2 pts vs this opponent (+3.7 vs line) — supporting the OVER. His H2H avg of 16.2 pts is 3.5 above his season L30; His TS% shifts +4.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#17). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Pace dissent. Projection model targets 13.5 pts (1.0 pts above line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8161,40 +8005,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.599</v>
+        <v>0.576</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>12.2</v>
+        <v>24</v>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
-        <v>1.917</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>1.82</v>
+        <v>1.364</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Henderson has a H2H avg of 10.6 pts vs this opponent (-4.9 vs line) — supporting the UNDER. His H2H avg of 10.6 pts is 3.2 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Pace against. Projection model targets 12.2 pts (3.3 pts below line; 59% blended confidence).</t>
+          <t>Jokić's L30 average of 26.0 pts vs line of 27.5, supports the UNDER. His H2H avg of 29.2 pts is 3.2 above his season L30; His TS% shifts +6.2% in this matchup. Opponent ranks as weak defense (#28) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 24.0 pts (3.5 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=8.9) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8204,7 +8048,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8213,36 +8057,36 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.539</v>
+        <v>0.598</v>
       </c>
       <c r="F58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>13.4</v>
+        <v>23.1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
-        <v>1.885</v>
+        <v>2.8</v>
       </c>
       <c r="K58" t="n">
-        <v>1.847</v>
+        <v>1.408</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Johnson has a H2H avg of 16.2 pts vs this opponent (+3.7 vs line) — supporting the OVER. His H2H avg of 16.2 pts is 3.5 above his season L30; His TS% shifts +4.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). 7/10 signals agree (Volume, HR L10, Trend, Context among the strongest); HR L30, Pace dissent. Projection model targets 13.4 pts (0.9 pts above line; 53% blended confidence).</t>
+          <t>Avdija has a H2H avg of 20.9 pts vs this opponent (-4.6 vs line) — supporting the UNDER. His TS% shifts +7.4% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 23.1 pts (2.4 pts below line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8261,125 +8105,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.553</v>
+        <v>0.514</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>25</v>
+        <v>17.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K59" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Jokić's L30 average of 26.0 pts vs line of 27.5, supports the UNDER. His H2H avg of 29.2 pts is 3.2 above his season L30; His TS% shifts +6.2% in this matchup. Opponent ranks as weak defense (#28) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 25.0 pts (2.5 pts below line; 55% blended confidence). Risk: high scoring volatility (σ=8.9) introduces outcome uncertainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1.877</v>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Avdija has a H2H avg of 20.9 pts vs this opponent (-4.6 vs line) — supporting the UNDER. His TS% shifts +7.4% in this matchup. Opponent ranks as below-average defense (#20) with fast pace (#3). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 23.2 pts (2.3 pts below line; 59% blended confidence).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F61" t="n">
-        <v>6</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>Holiday has a H2H avg of 14.5 pts vs this opponent (-4.0 vs line) — supporting the UNDER. His H2H avg of 14.5 pts is 2.5 below his season L30. Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — Volume, HR L10, Context support under; HR L30, Trend against. Projection model targets 16.9 pts (1.6 pts below line; 54% blended confidence). Risk: L3 has surged to 22.7 after a 22-pt performance (5.7 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Holiday has a H2H avg of 14.5 pts vs this opponent (-3.0 vs line) — supporting the UNDER. His H2H avg of 14.5 pts is 2.5 below his season L30. Opponent ranks as average defense (#11) with fast pace (#3). 6/10 signals agree — Volume, HR L10, Context support under; HR L30, Trend against. Projection model targets 17.1 pts (0.4 pts below line; 51% blended confidence). Risk: L3 has surged to 22.7 after a 22-pt performance (5.7 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8462,11 +8210,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="3">
@@ -8492,7 +8240,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8502,17 +8250,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8522,17 +8270,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8542,17 +8290,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8562,17 +8310,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8582,17 +8330,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8602,17 +8350,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8626,13 +8374,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8642,17 +8390,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8662,17 +8410,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8682,17 +8430,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8702,17 +8450,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8726,13 +8474,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8742,7 +8490,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -8752,7 +8500,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8762,17 +8510,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8782,17 +8530,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8802,17 +8550,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8822,17 +8570,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8846,13 +8594,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8866,13 +8614,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8886,13 +8634,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8902,17 +8650,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8926,13 +8674,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8946,13 +8694,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8966,13 +8714,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8986,7 +8734,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="29">
@@ -9062,7 +8810,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -9092,12 +8840,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9106,18 +8854,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9126,13 +8874,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9142,17 +8890,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9166,13 +8914,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9182,17 +8930,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9206,13 +8954,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9222,17 +8970,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9252,7 +9000,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9262,17 +9010,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9282,17 +9030,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9302,17 +9050,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9322,17 +9070,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9346,18 +9094,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9366,33 +9114,33 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9412,7 +9160,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9422,17 +9170,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9442,17 +9190,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9466,13 +9214,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9482,17 +9230,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9506,13 +9254,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9522,17 +9270,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9552,7 +9300,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9566,13 +9314,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9582,17 +9330,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9606,47 +9354,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1195,7 +1209,7 @@
         <v>-4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1285,7 +1299,6 @@
       <c r="V10" t="n">
         <v>27</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-6.4</v>
       </c>
@@ -3085,7 +3098,6 @@
       <c r="V32" t="n">
         <v>7</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
         <v>11.4</v>
       </c>
@@ -3163,7 +3175,6 @@
       <c r="V33" t="n">
         <v>7</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>0.8</v>
       </c>
@@ -3241,7 +3252,6 @@
       <c r="V34" t="n">
         <v>9</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-17.8</v>
       </c>
@@ -3401,7 +3411,6 @@
       <c r="V36" t="n">
         <v>9</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>-25.8</v>
       </c>
@@ -3479,7 +3488,6 @@
       <c r="V37" t="n">
         <v>9</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>-2</v>
       </c>
@@ -3639,7 +3647,6 @@
       <c r="V39" t="n">
         <v>9</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>-33.6</v>
       </c>
@@ -3709,7 +3716,7 @@
         <v>0.3</v>
       </c>
       <c r="T40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>21</v>
@@ -3717,7 +3724,6 @@
       <c r="V40" t="n">
         <v>23</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>5.9</v>
       </c>
@@ -3877,7 +3883,6 @@
       <c r="V42" t="n">
         <v>23</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>30.1</v>
       </c>
@@ -3955,7 +3960,6 @@
       <c r="V43" t="n">
         <v>9</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>-4.6</v>
       </c>
@@ -4197,7 +4201,6 @@
       <c r="V46" t="n">
         <v>9</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-13.1</v>
       </c>
@@ -4340,7 +4343,7 @@
         <v>35</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>-2.3</v>
@@ -8198,443 +8201,1015 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 14.5 line, -2.5). Projection model called 13.6 pts — actual 12 was 1.6 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (22 pts vs 15.5 line, +6.5). Projection model targeted 14.3 pts (correct direction) but actual was 22. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (2 pts vs 12.5 line, -10.5). Underperformed by 10.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (36 pts vs 19.5 line, +16.5).</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (30 pts vs 25.5 line, +4.5). Projection model (25.1 pts) and actual (30) both missed the mark. Key signals that disagreed: HR L10, Trend, Defense. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 17.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (21 pts vs 19.5 line, +1.5). Projection model called 23.2 pts — actual 21 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Landry Shamet</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (1 pts vs 8.5 line, -7.5).</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 10.5 line, -5.5). Projection model called 5.9 pts — actual 5 was 0.9 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 11.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 5.5 line, -2.5). Projection model targeted 8.6 pts (correct direction) but actual was 3. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (21 pts vs 21.5 line, -0.5). Projection model called 18.5 pts — actual 21 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (15 pts vs 12.5 line, +2.5). Projection model called 12.6 pts — actual 15 was 2.4 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (31 pts vs 22.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, H2H.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 9.5 line, +2.5). Projection model called 12.7 pts — actual 12 was 0.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 11.5 line, +0.5). Projection model called 11.6 pts — actual 12 was 0.4 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 14.5 line, -2.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (0 pts vs 7.5 line, -7.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 19.5 line, +5.5). Projection model called 22.5 pts — actual 25 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 22.5 line, -4.5). Projection model called 19.7 pts — actual 18 was 1.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 17.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 9.5 line, -1.5). Projection model called 8.3 pts — actual 8 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -8656,6 +9231,18 @@
       <c r="D24" t="n">
         <v>10.5</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8676,45 +9263,109 @@
       <c r="D25" t="n">
         <v>14.5</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (9 pts vs 8.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>10.5</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 10.5 line, +6.5). Projection model targeted 8.1 pts (correct direction) but actual was 17. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -8736,25 +9387,63 @@
       <c r="D28" t="n">
         <v>9.5</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>19.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (24 pts vs 19.5 line, +4.5). Projection model called 22.2 pts — actual 24 was 1.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -8776,25 +9465,63 @@
       <c r="D30" t="n">
         <v>19.5</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>14.5</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (13 pts vs 14.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -8816,6 +9543,18 @@
       <c r="D32" t="n">
         <v>11.5</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8836,525 +9575,1213 @@
       <c r="D33" t="n">
         <v>25.5</v>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 10.5 line, -5.5).</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 18.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 12.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (15 pts vs 25.5 line, -10.5).</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 15.5 line, -2.5). Projection model called 13.8 pts — actual 13 was 0.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (6 pts vs 5.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 28.5 line, -11.5). Projection model called 17.9 pts — actual 17 was 0.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 12.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 11.5 line, +5.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (16 pts vs 17.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (7 pts vs 10.5 line, -3.5). Projection model (11.1 pts) and actual (7) both missed the mark. Key signals that disagreed: H2H, Pace. Counter-signals that proved correct: H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (9 pts vs 13.5 line, -4.5). Projection model (13.9 pts) and actual (9) both missed the mark. Key signals that disagreed: Volume, HR L10, Trend. Counter-signals that proved correct: Volume, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (34 pts vs 27.5 line, +6.5). Projection model targeted 10.5 pts (correct direction) but actual was 34. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 15.5 line, +7.5). Projection model targeted 11.6 pts (correct direction) but actual was 23. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 7.5 line, -1.5). Projection model called 5.0 pts — actual 6 was 1.0 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (30 pts vs 14.5 line, +15.5). Overperformed by 15.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 11.5 line, -8.5). Underperformed by 8.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L10, Trend, Pace.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 12.5 line, +5.5). Projection model called 15.9 pts — actual 18 was 2.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 7.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, Pace, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (20 pts vs 24.5 line, -4.5). Projection model (24.2 pts) and actual (20) both missed the mark. Key signals that disagreed: HR L30, HR L10, Pace. Counter-signals that proved correct: HR L30, HR L10, Pace.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 11.5 line, -3.5). Projection model targeted 13.3 pts (correct direction) but actual was 8. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Pace, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 14.5 line, +3.5). Projection model targeted 11.2 pts (correct direction) but actual was 18. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Pace, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 12.5 line, +4.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (35 pts vs 27.5 line, +7.5). Projection model targeted 24.0 pts (correct direction) but actual was 35. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (26 pts vs 25.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 17.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, Trend, Pace.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
   </sheetData>
